--- a/data/file_generation/input/data_212/AI_项目不同阶段收益估算.xlsx
+++ b/data/file_generation/input/data_212/AI_项目不同阶段收益估算.xlsx
@@ -970,18 +970,26 @@
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
+  <documentManagement>
+    <SharedWithUsers xmlns="eca6eae4-1627-4e8d-9a6b-5b4dd91506e7">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </SharedWithUsers>
+  </documentManagement>
 </p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5240E571-1A20-4CB4-A21D-44A2D197601A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D46E475C-5F31-4435-837D-18904BCD7452}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BB1D9C06-5860-4409-A2E0-E36AF8015029}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E8DDF39A-18F7-48F7-B226-A147731748F9}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FDB3D704-A018-41A4-843F-C1174DAB61E0}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{583C48C3-A146-44AB-BF3C-1B0746BC400A}"/>
 </file>